--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1052,6 +1052,107 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127322100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bergalyckan 100m S, Råsarna  Holmahult, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>507601</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6310748</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dädesjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -1057,7 +1057,7 @@
         <v>127322100</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -1057,7 +1057,7 @@
         <v>127322100</v>
       </c>
       <c r="B5" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -1057,7 +1057,7 @@
         <v>127322100</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -1057,7 +1057,7 @@
         <v>127322100</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1153,6 +1153,216 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128889126</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bergalyckan s, Råsarna  Holmahult, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>507717</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6310624</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dädesjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128889093</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92825</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bergalyckan s, Råsarna  Holmahult, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>507717</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6310624</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dädesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>128889093</v>
       </c>
       <c r="B7" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -1158,7 +1158,7 @@
         <v>128889126</v>
       </c>
       <c r="B6" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>128889093</v>
       </c>
       <c r="B7" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -1158,7 +1158,7 @@
         <v>128889126</v>
       </c>
       <c r="B6" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>128889093</v>
       </c>
       <c r="B7" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>128889093</v>
       </c>
       <c r="B7" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>128889093</v>
       </c>
       <c r="B7" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -1158,7 +1158,7 @@
         <v>128889126</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>128889093</v>
       </c>
       <c r="B7" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>128889093</v>
       </c>
       <c r="B7" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -1158,7 +1158,7 @@
         <v>128889126</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>128889093</v>
       </c>
       <c r="B7" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>128889093</v>
       </c>
       <c r="B7" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>128889093</v>
       </c>
       <c r="B7" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>128889093</v>
       </c>
       <c r="B7" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127322100</v>
+        <v>128889126</v>
       </c>
       <c r="B5" t="n">
-        <v>57832</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,14 +1089,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergalyckan 100m S, Råsarna  Holmahult, Sm</t>
+          <t>Bergalyckan s, Råsarna  Holmahult, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507601</v>
+        <v>507717</v>
       </c>
       <c r="R5" t="n">
-        <v>6310748</v>
+        <v>6310624</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128889126</v>
+        <v>128889093</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>92863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,27 +1166,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1238,6 +1245,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1253,115 +1261,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>128889093</v>
-      </c>
-      <c r="B7" t="n">
-        <v>92863</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Bergalyckan s, Råsarna  Holmahult, Sm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>507717</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6310624</v>
-      </c>
-      <c r="S7" t="n">
-        <v>25</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Kronoberg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Växjö</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Dädesjö</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Tomas Lundqvist</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Tomas Lundqvist</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -1368,7 +1368,7 @@
         <v>72561755</v>
       </c>
       <c r="B8" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66910345</v>
+        <v>128889093</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergalyckan 100m S, Råsarna  Holmahult, Sm</t>
+          <t>Bergalyckan s, Råsarna  Holmahult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507600.5532686216</v>
+        <v>507717</v>
       </c>
       <c r="R2" t="n">
-        <v>6310748.308993606</v>
+        <v>6310624</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,27 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-07-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-07-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Både blommande och överblommade.</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66910171</v>
+        <v>124350795</v>
       </c>
       <c r="B3" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,16 +795,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,32 +817,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergalyckan 100m S, Råsarna  Holmahult, Sm</t>
+          <t>Magersryd, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507600.5532686216</v>
+        <v>507952</v>
       </c>
       <c r="R3" t="n">
-        <v>6310748.308993606</v>
+        <v>6310311</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,22 +858,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-07-29</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-07-29</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,27 +888,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Ellen Flygare</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Ellen Flygare</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100958384</v>
+        <v>72561755</v>
       </c>
       <c r="B4" t="n">
-        <v>55649</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208255</v>
+        <v>102626</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -966,14 +933,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -981,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507600.5532686216</v>
+        <v>507601</v>
       </c>
       <c r="R4" t="n">
-        <v>6310748.308993606</v>
+        <v>6310748</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,22 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-08-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-08-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,7 +999,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1057,7 +1020,7 @@
         <v>127322100</v>
       </c>
       <c r="B5" t="n">
-        <v>57832</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1121,7 @@
         <v>128889126</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,56 +1219,62 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128889093</v>
+        <v>66910171</v>
       </c>
       <c r="B7" t="n">
-        <v>92863</v>
+        <v>58817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergalyckan s, Råsarna  Holmahult, Sm</t>
+          <t>Bergalyckan 100m S, Råsarna  Holmahult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507717</v>
+        <v>507601</v>
       </c>
       <c r="R7" t="n">
-        <v>6310624</v>
+        <v>6310748</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1332,12 +1301,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2017-07-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2017-07-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,7 +1315,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1365,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>72561755</v>
+        <v>100958384</v>
       </c>
       <c r="B8" t="n">
-        <v>58035</v>
+        <v>56884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,21 +1344,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102626</v>
+        <v>208255</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1398,21 +1366,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1450,12 +1411,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-08-04</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-08-04</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,6 +1425,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1479,6 +1441,115 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>66910345</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bergalyckan 100m S, Råsarna  Holmahult, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>507601</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6310748</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dädesjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-07-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-07-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Både blommande och överblommade.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128889093</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124350795</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72561755</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127322100</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128889126</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66910171</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100958384</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1550,8 +1590,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66910345</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>